--- a/data/trans_orig/IP1003-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP1003-Provincia-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4236</t>
+          <t>4357</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1427</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7850</t>
+          <t>8554</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2096</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9719</t>
+          <t>10216</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48332</t>
+          <t>48211</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52367</t>
+          <t>51663</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58790</t>
+          <t>58713</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>103066</t>
+          <t>102569</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>110726</t>
+          <t>110689</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,14%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7694</t>
+          <t>7516</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>2440</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9397</t>
+          <t>9778</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4901</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14380</t>
+          <t>14278</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>93868</t>
+          <t>94046</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>100296</t>
+          <t>99766</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>99360</t>
+          <t>98979</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>106754</t>
+          <t>106317</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>195939</t>
+          <t>196041</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>205418</t>
+          <t>205259</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,59%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2133</t>
+          <t>2203</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10079</t>
+          <t>9596</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1156</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6756</t>
+          <t>6769</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4199</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13526</t>
+          <t>13655</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,9%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>57518</t>
+          <t>58001</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>65464</t>
+          <t>65394</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>63571</t>
+          <t>63558</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>69162</t>
+          <t>69171</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>124398</t>
+          <t>124269</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>133725</t>
+          <t>133812</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,02%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4397</t>
+          <t>4743</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13198</t>
+          <t>13443</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5010</t>
+          <t>5414</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14073</t>
+          <t>15040</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12051</t>
+          <t>12248</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24353</t>
+          <t>24382</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,84%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>61663</t>
+          <t>61418</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>70464</t>
+          <t>70118</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>65038</t>
+          <t>64071</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>74101</t>
+          <t>73697</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>129619</t>
+          <t>129590</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>141921</t>
+          <t>141724</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,05%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2307</t>
+          <t>2283</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10355</t>
+          <t>10066</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6649</t>
+          <t>6332</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3941</t>
+          <t>4159</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13398</t>
+          <t>13105</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,12%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31497</t>
+          <t>31786</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39545</t>
+          <t>39569</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38194</t>
+          <t>38511</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>73297</t>
+          <t>73590</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>82754</t>
+          <t>82536</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,2%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>700</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6225</t>
+          <t>6232</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4360</t>
+          <t>4408</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12098</t>
+          <t>12817</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6304</t>
+          <t>6286</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15987</t>
+          <t>15484</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,37%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>49830</t>
+          <t>49823</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>55357</t>
+          <t>55355</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>47634</t>
+          <t>46915</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>55372</t>
+          <t>55324</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>99800</t>
+          <t>100303</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>109483</t>
+          <t>109501</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,57%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2101</t>
+          <t>2086</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9209</t>
+          <t>9343</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>4184</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13173</t>
+          <t>13843</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7586</t>
+          <t>7636</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18401</t>
+          <t>19531</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>119413</t>
+          <t>119279</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>126521</t>
+          <t>126536</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>122482</t>
+          <t>121812</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>131605</t>
+          <t>131471</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>245876</t>
+          <t>244746</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>256691</t>
+          <t>256641</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,11%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5139</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14536</t>
+          <t>14903</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7147</t>
+          <t>7371</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>17854</t>
+          <t>18141</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>28017</t>
+          <t>28285</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,79%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>143368</t>
+          <t>143001</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>152765</t>
+          <t>152645</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>146204</t>
+          <t>145917</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>156911</t>
+          <t>156687</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>293945</t>
+          <t>293677</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>32109</t>
+          <t>30846</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>51320</t>
+          <t>51436</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>40194</t>
+          <t>39158</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>61202</t>
+          <t>60760</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>76829</t>
+          <t>77445</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>107294</t>
+          <t>107716</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>629701</t>
+          <t>629585</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>648912</t>
+          <t>650175</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>661498</t>
+          <t>661940</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>682506</t>
+          <t>683542</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1296427</t>
+          <t>1296005</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1326892</t>
+          <t>1326276</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,48%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7103</t>
+          <t>7962</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1829</t>
+          <t>1741</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10411</t>
+          <t>9928</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4077</t>
+          <t>4210</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13883</t>
+          <t>13846</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,18%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45861</t>
+          <t>45002</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51951</t>
+          <t>51675</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50350</t>
+          <t>50833</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58932</t>
+          <t>59020</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>99842</t>
+          <t>99879</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>109648</t>
+          <t>109515</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,3%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3652</t>
+          <t>3993</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12508</t>
+          <t>12660</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3721</t>
+          <t>3358</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12900</t>
+          <t>12103</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8859</t>
+          <t>8577</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21519</t>
+          <t>20719</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>91578</t>
+          <t>91426</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>100434</t>
+          <t>100093</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>98259</t>
+          <t>99056</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>107438</t>
+          <t>107801</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>193726</t>
+          <t>194526</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>206386</t>
+          <t>206668</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>96,02%</t>
         </is>
       </c>
     </row>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4969</t>
+          <t>4834</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>642</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6087</t>
+          <t>6063</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>990</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8028</t>
+          <t>7980</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63209</t>
+          <t>63344</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>64497</t>
+          <t>64521</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>69939</t>
+          <t>69942</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>130734</t>
+          <t>130782</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>137394</t>
+          <t>137772</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1546</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9608</t>
+          <t>9304</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2774</t>
+          <t>3121</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10914</t>
+          <t>10884</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5766</t>
+          <t>5723</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15947</t>
+          <t>16598</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,37%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>68153</t>
+          <t>68457</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>76215</t>
+          <t>76265</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>71320</t>
+          <t>71350</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>79460</t>
+          <t>79113</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>144048</t>
+          <t>143397</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>154229</t>
+          <t>154272</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,42%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>899</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7434</t>
+          <t>7469</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>658</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6142</t>
+          <t>6127</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2764</t>
+          <t>2834</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10298</t>
+          <t>10798</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>12,0%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36467</t>
+          <t>36432</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43046</t>
+          <t>43002</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>39963</t>
+          <t>39978</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>45444</t>
+          <t>45447</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>79708</t>
+          <t>79208</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>87242</t>
+          <t>87172</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,85%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>1194</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7330</t>
+          <t>7084</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3300</t>
+          <t>3648</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11827</t>
+          <t>12156</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5518</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16300</t>
+          <t>16199</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,94%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>48655</t>
+          <t>48901</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>54748</t>
+          <t>54791</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>48418</t>
+          <t>48089</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>56945</t>
+          <t>56597</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>99930</t>
+          <t>100031</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>110712</t>
+          <t>110230</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>94,84%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2730</t>
+          <t>2722</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10058</t>
+          <t>10920</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3585</t>
+          <t>3874</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12823</t>
+          <t>12349</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7920</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>20206</t>
+          <t>19500</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>128660</t>
+          <t>127798</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>135988</t>
+          <t>135996</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>132916</t>
+          <t>133390</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>142154</t>
+          <t>141865</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>264251</t>
+          <t>264957</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>276537</t>
+          <t>276405</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,17%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>1962</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9126</t>
+          <t>8929</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5204</t>
+          <t>5349</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15548</t>
+          <t>15035</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8945</t>
+          <t>8860</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>20771</t>
+          <t>20858</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>155582</t>
+          <t>155779</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>162693</t>
+          <t>162746</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>155767</t>
+          <t>156280</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>166111</t>
+          <t>165966</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>315252</t>
+          <t>315165</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>327078</t>
+          <t>327163</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,36%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>24255</t>
+          <t>24901</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>43089</t>
+          <t>44335</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,47 +6815,47 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
+          <t>6,28%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>45668</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>35045</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>56959</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
           <t>6,1%</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>45668</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>34688</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>57298</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>6,1%</t>
-        </is>
-      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>65827</t>
+          <t>65552</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>94505</t>
+          <t>95580</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>663212</t>
+          <t>661966</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>682046</t>
+          <t>681400</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,47 +6928,47 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>93,72%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>96,47%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>702474</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>691183</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>713097</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
           <t>93,9%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>96,57%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1001</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>702474</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>690844</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>713454</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>93,9%</t>
-        </is>
-      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1359938</t>
+          <t>1358863</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1388616</t>
+          <t>1388891</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,49%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8857</t>
+          <t>9428</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1795</t>
+          <t>1875</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9525</t>
+          <t>10028</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5444</t>
+          <t>5456</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16294</t>
+          <t>16228</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,32%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48514</t>
+          <t>47943</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55389</t>
+          <t>55341</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54937</t>
+          <t>54434</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62667</t>
+          <t>62587</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>105539</t>
+          <t>105605</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>116389</t>
+          <t>116377</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,52%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2111</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9977</t>
+          <t>10225</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2203</t>
+          <t>2292</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10721</t>
+          <t>11148</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5919</t>
+          <t>5893</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17331</t>
+          <t>17257</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>93970</t>
+          <t>93722</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>101925</t>
+          <t>101836</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>99562</t>
+          <t>99135</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>108080</t>
+          <t>107991</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>196899</t>
+          <t>196973</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>208311</t>
+          <t>208337</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,25%</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5138</t>
+          <t>5155</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1385</t>
+          <t>1376</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7808</t>
+          <t>7837</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2160</t>
+          <t>2143</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10658</t>
+          <t>9618</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>61693</t>
+          <t>61676</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>62097</t>
+          <t>62068</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>68520</t>
+          <t>68529</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>126078</t>
+          <t>127118</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>134576</t>
+          <t>134593</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,43%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2442</t>
+          <t>2323</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9364</t>
+          <t>9255</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11639</t>
+          <t>11443</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17518</t>
+          <t>18267</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,55%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>67597</t>
+          <t>67706</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>74519</t>
+          <t>74638</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>69545</t>
+          <t>69741</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>78292</t>
+          <t>77741</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>140627</t>
+          <t>139878</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>151198</t>
+          <t>151239</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,63%</t>
         </is>
       </c>
     </row>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4691</t>
+          <t>4008</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3577</t>
+          <t>3996</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>5128</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38747</t>
+          <t>39430</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8899,7 +8899,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>42773</t>
+          <t>42354</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>84640</t>
+          <t>84660</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1925</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8671</t>
+          <t>9765</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3298</t>
+          <t>3256</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11985</t>
+          <t>12028</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6366</t>
+          <t>6375</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17295</t>
+          <t>17893</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,97%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>45602</t>
+          <t>44508</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>52348</t>
+          <t>52254</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>45754</t>
+          <t>45711</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>54441</t>
+          <t>54483</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>94717</t>
+          <t>94119</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>105646</t>
+          <t>105637</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,31%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1344</t>
+          <t>1317</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>8116</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1324</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8174</t>
+          <t>7543</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3471</t>
+          <t>3695</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13715</t>
+          <t>12851</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>129278</t>
+          <t>129258</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>136030</t>
+          <t>136057</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>135898</t>
+          <t>136529</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>142748</t>
+          <t>142756</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>267731</t>
+          <t>268595</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>277975</t>
+          <t>277751</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4070</t>
+          <t>3499</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>11825</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4310</t>
+          <t>4083</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12888</t>
+          <t>12585</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9587</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>21966</t>
+          <t>21580</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>150834</t>
+          <t>152351</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>160106</t>
+          <t>160677</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>157961</t>
+          <t>158264</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>166539</t>
+          <t>166766</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>313059</t>
+          <t>313445</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>325438</t>
+          <t>325506</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,16%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>23846</t>
+          <t>23611</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>43540</t>
+          <t>41695</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>29223</t>
+          <t>29652</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>50166</t>
+          <t>50237</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>58482</t>
+          <t>57546</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>86083</t>
+          <t>85532</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>660831</t>
+          <t>662676</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>680525</t>
+          <t>680760</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>694678</t>
+          <t>694607</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>715621</t>
+          <t>715192</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1363132</t>
+          <t>1363683</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1390733</t>
+          <t>1391669</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,03%</t>
         </is>
       </c>
     </row>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1813</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8761</t>
+          <t>9233</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,47 +10717,47 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>12,6%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>4563</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1960</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>9775</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>5,75%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
           <t>2,47%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,96%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4563</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1947</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>9703</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>5,75%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4972</t>
+          <t>4861</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15327</t>
+          <t>15101</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,89%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>64521</t>
+          <t>64049</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>71469</t>
+          <t>71341</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,49 +10830,49 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>97,35%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>74803</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>69591</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>77406</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>94,25%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>87,68%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
           <t>97,53%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>74803</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>69663</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>77419</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>94,25%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>87,77%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>97,55%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>185</t>
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>137321</t>
+          <t>137547</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>147676</t>
+          <t>147787</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,82%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>2576</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14571</t>
+          <t>14067</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3156</t>
+          <t>3237</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14103</t>
+          <t>13866</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8461</t>
+          <t>8254</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22737</t>
+          <t>23401</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,29%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>111437</t>
+          <t>111941</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>123063</t>
+          <t>123432</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>111699</t>
+          <t>111936</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>122646</t>
+          <t>122565</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>229073</t>
+          <t>228409</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>243349</t>
+          <t>243556</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,72%</t>
         </is>
       </c>
     </row>
@@ -11393,7 +11393,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>2954</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11408,7 +11408,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8196</t>
+          <t>7889</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1938</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8893</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -11501,7 +11501,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54610</t>
+          <t>55314</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58967</t>
+          <t>59274</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>65296</t>
+          <t>65687</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>116538</t>
+          <t>116431</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>123497</t>
+          <t>123493</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,7 +11586,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>854</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8967</t>
+          <t>8799</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1437</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13019</t>
+          <t>13401</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3890</t>
+          <t>3777</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17109</t>
+          <t>16624</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,26%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>60551</t>
+          <t>60719</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>68443</t>
+          <t>68664</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>65115</t>
+          <t>64733</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>76697</t>
+          <t>76692</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>130544</t>
+          <t>131029</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>143763</t>
+          <t>143876</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,44%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>454</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3924</t>
+          <t>4175</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1174</t>
+          <t>1166</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10306</t>
+          <t>10852</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2570</t>
+          <t>2594</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12253</t>
+          <t>13145</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>17,47%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30589</t>
+          <t>30338</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34055</t>
+          <t>34059</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30413</t>
+          <t>29867</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39545</t>
+          <t>39553</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>62979</t>
+          <t>62087</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>72662</t>
+          <t>72638</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,55%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3382</t>
+          <t>3471</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11136</t>
+          <t>11013</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5305</t>
+          <t>5571</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15858</t>
+          <t>15903</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11116</t>
+          <t>11214</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24501</t>
+          <t>23650</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,11%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>35031</t>
+          <t>35154</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>42785</t>
+          <t>42696</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>40328</t>
+          <t>40283</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>50881</t>
+          <t>50615</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>77852</t>
+          <t>78703</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>91237</t>
+          <t>91139</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,04%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5609</t>
+          <t>5360</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16346</t>
+          <t>16298</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13659</t>
+          <t>13703</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32189</t>
+          <t>33343</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>21785</t>
+          <t>22248</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>41974</t>
+          <t>43424</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,48%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>108162</t>
+          <t>108210</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>118899</t>
+          <t>119148</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>123823</t>
+          <t>122669</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>142353</t>
+          <t>142309</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>238546</t>
+          <t>237096</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>258735</t>
+          <t>258272</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,07%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>601</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5810</t>
+          <t>5656</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,47 +13118,47 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>4,3%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>6907</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>3198</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>13183</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
           <t>4,41%</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>6907</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>3432</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>13276</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>4,41%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4698</t>
+          <t>4606</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15034</t>
+          <t>14856</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>125809</t>
+          <t>125963</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>131038</t>
+          <t>131018</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,47 +13231,47 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>95,7%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>99,54%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>149888</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>143612</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>153597</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
           <t>95,59%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>99,56%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>149888</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>143519</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>153363</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>95,59%</t>
-        </is>
-      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>273380</t>
+          <t>273558</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>283716</t>
+          <t>283808</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>26562</t>
+          <t>27416</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>47281</t>
+          <t>50068</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>49192</t>
+          <t>49293</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>80052</t>
+          <t>79927</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>82784</t>
+          <t>79215</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>119073</t>
+          <t>118587</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>616603</t>
+          <t>613816</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>637322</t>
+          <t>636468</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>680125</t>
+          <t>680250</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>710985</t>
+          <t>710884</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1304989</t>
+          <t>1305475</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1341278</t>
+          <t>1344847</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,44%</t>
         </is>
       </c>
     </row>
